--- a/template/Product_Category_Template.xlsx
+++ b/template/Product_Category_Template.xlsx
@@ -32,7 +32,7 @@
     <t>Category Name</t>
   </si>
   <si>
-    <t>Entity Type</t>
+    <t>Post To SQL</t>
   </si>
 </sst>
 </file>
@@ -45,20 +45,13 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -522,155 +515,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1010,27 +1002,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="12.8296296296296" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="11.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:3">
+    <row r="1" ht="15.75" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>"Supplier, Customer"</formula1>
+      <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/template/Product_Category_Template.xlsx
+++ b/template/Product_Category_Template.xlsx
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>Company</t>
+  </si>
   <si>
     <t>Category Name</t>
   </si>
@@ -1002,24 +1005,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="12.8296296296296" customWidth="1"/>
-    <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.8296296296296" customWidth="1"/>
+    <col min="3" max="3" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:2">
+    <row r="1" ht="15.75" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/template/Product_Category_Template.xlsx
+++ b/template/Product_Category_Template.xlsx
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Company</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>Category Name</t>
   </si>
@@ -1005,27 +1002,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="2" max="2" width="12.8296296296296" customWidth="1"/>
-    <col min="3" max="3" width="11.6666666666667" customWidth="1"/>
+    <col min="1" max="1" width="12.8296296296296" customWidth="1"/>
+    <col min="2" max="2" width="11.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:3">
+    <row r="1" ht="15.75" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
